--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486366_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486366_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2825</v>
+        <v>-0.1408</v>
       </c>
       <c r="E2" t="n">
-        <v>0.613</v>
+        <v>0.5698</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8955</v>
+        <v>-0.7106</v>
       </c>
       <c r="G2" t="n">
         <v>-0.8889</v>
@@ -610,13 +610,13 @@
         <v>1.5225</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2636</v>
+        <v>-0.122</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0517</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2552</v>
+        <v>-0.0703</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-2.3623</v>
+        <v>-2.2359</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.7</v>
+        <v>-2.2962</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3377</v>
+        <v>0.0603</v>
       </c>
       <c r="G3" t="n">
         <v>-1.9167</v>
@@ -688,13 +688,13 @@
         <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>0.077</v>
+        <v>0.2034</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.2812</v>
       </c>
       <c r="U3" t="n">
-        <v>0.762</v>
+        <v>0.4846</v>
       </c>
       <c r="V3" t="n">
         <v>0.5649999999999999</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. CAMACHO DE SÁ</t>
+          <t>D. AGBELESE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.4152</v>
+        <v>-2.4344</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6989</v>
+        <v>-1.3553</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.7163</v>
+        <v>-1.0792</v>
       </c>
       <c r="G4" t="n">
-        <v>-5.071</v>
+        <v>-0.8417</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2014</v>
+        <v>-0.0305</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.8695</v>
+        <v>-0.8112</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.7758</v>
+        <v>0.0747</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4594</v>
+        <v>0.0365</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.2352</v>
+        <v>0.0382</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.2952</v>
+        <v>-0.9164</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.6608</v>
+        <v>-0.067</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.6344</v>
+        <v>-0.8495</v>
       </c>
       <c r="P4" t="n">
         <v>-0.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.6101</v>
+        <v>-1.0875</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7401</v>
+        <v>0.2175</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0706</v>
+        <v>-0.3323</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2318</v>
+        <v>-0.3425</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1612</v>
+        <v>0.0102</v>
       </c>
       <c r="V4" t="n">
-        <v>2.4552</v>
+        <v>-0.3904</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4552</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. AGBELESE</t>
+          <t>A. COMENDADOR FEMENIAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.4413</v>
+        <v>-2.6548</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.4238</v>
+        <v>-1.6354</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0175</v>
+        <v>-1.0194</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8417</v>
+        <v>-1.4303</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0305</v>
+        <v>-0.2828</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8112</v>
+        <v>-1.1475</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0747</v>
+        <v>0.1492</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0365</v>
+        <v>0.1492</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0382</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9164</v>
+        <v>-1.5794</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.067</v>
+        <v>-0.432</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8495</v>
+        <v>-1.1475</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.87</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0875</v>
+        <v>-1.5225</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3391</v>
+        <v>-0.572</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.411</v>
+        <v>-0.262</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07190000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. COMENDADOR FEMENIAS</t>
+          <t>N. CAMACHO DE SÁ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.5315</v>
+        <v>-3.5817</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6354</v>
+        <v>-1.8345</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8962</v>
+        <v>-1.7471</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4303</v>
+        <v>-5.071</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2828</v>
+        <v>-1.2014</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1475</v>
+        <v>-3.8695</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1492</v>
+        <v>-1.7758</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1492</v>
+        <v>0.4594</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-2.2352</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5794</v>
+        <v>-3.2952</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.432</v>
+        <v>-1.6608</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1475</v>
+        <v>-1.6344</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6525</v>
+        <v>-0.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.5225</v>
+        <v>-2.6101</v>
       </c>
       <c r="R6" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4487</v>
+        <v>-0.0958</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.262</v>
+        <v>0.0961</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1867</v>
+        <v>-0.192</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>2.4552</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.4552</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. CARRALERO MARTIN</t>
+          <t>G. DIKE EGUN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.6724</v>
+        <v>-5.2028</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.9399</v>
+        <v>-2.4561</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.7324</v>
+        <v>-2.7467</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.3933</v>
+        <v>-1.1573</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.39</v>
+        <v>-2.3573</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.0033</v>
+        <v>1.2001</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.1604</v>
+        <v>2.201</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7086</v>
+        <v>0.365</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.4519</v>
+        <v>1.836</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2328</v>
+        <v>-3.3582</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6814</v>
+        <v>-2.7223</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5514</v>
+        <v>-0.6359</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.435</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.305</v>
+        <v>-4.1326</v>
       </c>
       <c r="R7" t="n">
-        <v>0.87</v>
+        <v>1.7401</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5189</v>
+        <v>-0.1532</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6044</v>
+        <v>0.2151</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0856</v>
+        <v>-0.3683</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3252</v>
+        <v>-1.4997</v>
       </c>
       <c r="W7" t="n">
-        <v>1.13</v>
+        <v>-0.7395</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.4552</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. DIKE EGUN</t>
+          <t>J. CARRALERO MARTIN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.8167</v>
+        <v>-5.2069</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.8851</v>
+        <v>-2.5362</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.9316</v>
+        <v>-2.6708</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1573</v>
+        <v>-3.3933</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.3573</v>
+        <v>-1.39</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2001</v>
+        <v>-2.0033</v>
       </c>
       <c r="J8" t="n">
-        <v>2.201</v>
+        <v>-2.1604</v>
       </c>
       <c r="K8" t="n">
-        <v>0.365</v>
+        <v>-0.7086</v>
       </c>
       <c r="L8" t="n">
-        <v>1.836</v>
+        <v>-1.4519</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.3582</v>
+        <v>-1.2328</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.7223</v>
+        <v>-0.6814</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6359</v>
+        <v>-0.5514</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.3926</v>
+        <v>-0.435</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.1326</v>
+        <v>-1.305</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7401</v>
+        <v>0.87</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7672</v>
+        <v>-0.0535</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2139</v>
+        <v>-0.2007</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5533</v>
+        <v>0.1472</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.4997</v>
+        <v>-1.3252</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.7395</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.7602</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.4073</v>
+        <v>-6.0536</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.6801</v>
+        <v>-3.3881</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.7271</v>
+        <v>-2.6655</v>
       </c>
       <c r="G9" t="n">
         <v>-4.7019</v>
@@ -1156,13 +1156,13 @@
         <v>1.7401</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3579</v>
+        <v>-0.0042</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2139</v>
+        <v>0.0781</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.144</v>
+        <v>-0.0823</v>
       </c>
       <c r="V9" t="n">
         <v>-1.13</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.6007</v>
+        <v>-6.2162</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8825</v>
+        <v>-2.5905</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.7182</v>
+        <v>-3.6257</v>
       </c>
       <c r="G10" t="n">
         <v>-2.3814</v>
@@ -1234,13 +1234,13 @@
         <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0019</v>
+        <v>-0.6173999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.536</v>
+        <v>-0.2439</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4659</v>
+        <v>-0.3734</v>
       </c>
       <c r="V10" t="n">
         <v>-1.695</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.3235</v>
+        <v>-7.8378</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.0729</v>
+        <v>-5.4947</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2507</v>
+        <v>-2.3431</v>
       </c>
       <c r="G11" t="n">
         <v>-6.3132</v>
@@ -1312,13 +1312,13 @@
         <v>1.7401</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2724</v>
+        <v>-0.2418</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6237</v>
+        <v>0.2019</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3513</v>
+        <v>-0.4437</v>
       </c>
       <c r="V11" t="n">
         <v>-0.1952</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-12.6207</v>
+        <v>-11.8872</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.7192</v>
+        <v>-6.9549</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.9015</v>
+        <v>-4.9323</v>
       </c>
       <c r="G12" t="n">
         <v>-6.8683</v>
@@ -1390,13 +1390,13 @@
         <v>1.7401</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3821</v>
+        <v>-0.6486</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0719</v>
+        <v>-0.3076</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3102</v>
+        <v>-0.341</v>
       </c>
       <c r="V12" t="n">
         <v>-1.3252</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-14.4443</v>
+        <v>-14.0963</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.9122</v>
+        <v>-9.595000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.5321</v>
+        <v>-4.5013</v>
       </c>
       <c r="G13" t="n">
         <v>-7.8364</v>
@@ -1468,13 +1468,13 @@
         <v>1.9576</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3904</v>
+        <v>-0.0424</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2704</v>
+        <v>0.0469</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1201</v>
+        <v>-0.0892</v>
       </c>
       <c r="V13" t="n">
         <v>-3.3899</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-68.91840000000001</v>
+        <v>-67.5484</v>
       </c>
       <c r="E14" t="n">
-        <v>-40.937</v>
+        <v>-39.5671</v>
       </c>
       <c r="F14" t="n">
         <v>-27.9814</v>
@@ -1546,16 +1546,16 @@
         <v>16.3131</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.049799999999999</v>
+        <v>-2.6798</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.4214</v>
+        <v>-1.0515</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.6284</v>
+        <v>-1.6282</v>
       </c>
       <c r="V14" t="n">
-        <v>-7.930399999999999</v>
+        <v>-7.9304</v>
       </c>
       <c r="W14" t="n">
         <v>4.540699999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>10.3139</v>
+        <v>9.7409</v>
       </c>
       <c r="E15" t="n">
-        <v>7.8799</v>
+        <v>6.7623</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4339</v>
+        <v>2.9785</v>
       </c>
       <c r="G15" t="n">
         <v>8.015000000000001</v>
@@ -1624,13 +1624,13 @@
         <v>2.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>1.449</v>
+        <v>0.876</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5502</v>
+        <v>0.4326</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1012</v>
+        <v>0.4434</v>
       </c>
       <c r="V15" t="n">
         <v>-1.3252</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. KRAVIC</t>
+          <t>A. BARCELLO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.9097</v>
+        <v>7.9684</v>
       </c>
       <c r="E16" t="n">
-        <v>4.8664</v>
+        <v>3.1623</v>
       </c>
       <c r="F16" t="n">
-        <v>3.0433</v>
+        <v>4.8061</v>
       </c>
       <c r="G16" t="n">
-        <v>5.4795</v>
+        <v>2.779</v>
       </c>
       <c r="H16" t="n">
-        <v>5.4047</v>
+        <v>0.955</v>
       </c>
       <c r="I16" t="n">
-        <v>0.07489999999999999</v>
+        <v>1.824</v>
       </c>
       <c r="J16" t="n">
-        <v>5.0238</v>
+        <v>0.7113</v>
       </c>
       <c r="K16" t="n">
-        <v>4.9091</v>
+        <v>0.8244</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1147</v>
+        <v>-0.1131</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4557</v>
+        <v>2.0678</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4956</v>
+        <v>0.1306</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0399</v>
+        <v>1.9371</v>
       </c>
       <c r="P16" t="n">
-        <v>1.305</v>
+        <v>2.3926</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.6101</v>
+        <v>2.3926</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1251</v>
+        <v>0.5369</v>
       </c>
       <c r="T16" t="n">
-        <v>1.1476</v>
+        <v>0.1911</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0225</v>
+        <v>0.3458</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.2599</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. DE SOUSA ANJO BRITO</t>
+          <t>L. WESTERMANN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>7.1698</v>
+        <v>7.4859</v>
       </c>
       <c r="E17" t="n">
-        <v>1.036</v>
+        <v>1.8483</v>
       </c>
       <c r="F17" t="n">
-        <v>6.1338</v>
+        <v>5.6377</v>
       </c>
       <c r="G17" t="n">
-        <v>3.1388</v>
+        <v>5.7457</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1563</v>
+        <v>2.0316</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9825</v>
+        <v>3.7142</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2385</v>
+        <v>4.1274</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2806</v>
+        <v>2.1169</v>
       </c>
       <c r="L17" t="n">
-        <v>0.9578</v>
+        <v>2.0105</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9003</v>
+        <v>1.6183</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8757</v>
+        <v>-0.0854</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0247</v>
+        <v>1.7037</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7401</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3926</v>
+        <v>-4.3501</v>
       </c>
       <c r="R17" t="n">
-        <v>4.1326</v>
+        <v>3.2626</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1609</v>
+        <v>0.7423</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0601</v>
+        <v>-0.0144</v>
       </c>
       <c r="U17" t="n">
-        <v>1.1009</v>
+        <v>0.7568</v>
       </c>
       <c r="V17" t="n">
-        <v>1.13</v>
+        <v>2.0854</v>
       </c>
       <c r="W17" t="n">
-        <v>1.13</v>
+        <v>2.0854</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. WESTERMANN</t>
+          <t>D. KRAVIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>6.8564</v>
+        <v>7.1724</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1777</v>
+        <v>4.1959</v>
       </c>
       <c r="F18" t="n">
-        <v>5.6787</v>
+        <v>2.9766</v>
       </c>
       <c r="G18" t="n">
-        <v>5.7457</v>
+        <v>5.4795</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0316</v>
+        <v>5.4047</v>
       </c>
       <c r="I18" t="n">
-        <v>3.7142</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>4.1274</v>
+        <v>5.0238</v>
       </c>
       <c r="K18" t="n">
-        <v>2.1169</v>
+        <v>4.9091</v>
       </c>
       <c r="L18" t="n">
-        <v>2.0105</v>
+        <v>0.1147</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6183</v>
+        <v>0.4557</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0854</v>
+        <v>0.4956</v>
       </c>
       <c r="O18" t="n">
-        <v>1.7037</v>
+        <v>-0.0399</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.3501</v>
+        <v>-1.305</v>
       </c>
       <c r="R18" t="n">
-        <v>3.2626</v>
+        <v>2.6101</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1128</v>
+        <v>0.3878</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0.4771</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7978</v>
+        <v>-0.0892</v>
       </c>
       <c r="V18" t="n">
-        <v>2.0854</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.0854</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. ANDERSSON</t>
+          <t>D. DE SOUSA ANJO BRITO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>6.7801</v>
+        <v>6.5841</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6759</v>
+        <v>1.036</v>
       </c>
       <c r="F19" t="n">
-        <v>5.1042</v>
+        <v>5.5482</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5589</v>
+        <v>3.1388</v>
       </c>
       <c r="H19" t="n">
-        <v>1.0066</v>
+        <v>2.1563</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5523</v>
+        <v>0.9825</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9071</v>
+        <v>2.2385</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0585</v>
+        <v>1.2806</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1514</v>
+        <v>0.9578</v>
       </c>
       <c r="M19" t="n">
-        <v>1.6518</v>
+        <v>0.9003</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0519</v>
+        <v>0.8757</v>
       </c>
       <c r="O19" t="n">
-        <v>1.7037</v>
+        <v>0.0247</v>
       </c>
       <c r="P19" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1751</v>
+        <v>-2.3926</v>
       </c>
       <c r="R19" t="n">
-        <v>3.4801</v>
+        <v>4.1326</v>
       </c>
       <c r="S19" t="n">
-        <v>1.4164</v>
+        <v>0.5753</v>
       </c>
       <c r="T19" t="n">
-        <v>1.6187</v>
+        <v>0.0601</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2023</v>
+        <v>0.5152</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4997</v>
+        <v>1.13</v>
       </c>
       <c r="W19" t="n">
-        <v>1.3252</v>
+        <v>1.13</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. BARCELLO</t>
+          <t>R. ANDERSSON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>6.7224</v>
+        <v>6.0273</v>
       </c>
       <c r="E20" t="n">
-        <v>2.4917</v>
+        <v>0.5583</v>
       </c>
       <c r="F20" t="n">
-        <v>4.2307</v>
+        <v>5.4689</v>
       </c>
       <c r="G20" t="n">
-        <v>2.779</v>
+        <v>2.5589</v>
       </c>
       <c r="H20" t="n">
-        <v>0.955</v>
+        <v>1.0066</v>
       </c>
       <c r="I20" t="n">
-        <v>1.824</v>
+        <v>1.5523</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7113</v>
+        <v>0.9071</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8244</v>
+        <v>1.0585</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1131</v>
+        <v>-0.1514</v>
       </c>
       <c r="M20" t="n">
-        <v>2.0678</v>
+        <v>1.6518</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1306</v>
+        <v>-0.0519</v>
       </c>
       <c r="O20" t="n">
-        <v>1.9371</v>
+        <v>1.7037</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3926</v>
+        <v>1.305</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3926</v>
+        <v>3.4801</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7091</v>
+        <v>0.6636</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4795</v>
+        <v>0.5011</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2297</v>
+        <v>0.1625</v>
       </c>
       <c r="V20" t="n">
-        <v>2.2599</v>
+        <v>1.4997</v>
       </c>
       <c r="W20" t="n">
-        <v>2.2599</v>
+        <v>1.3252</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>4.6063</v>
+        <v>5.4066</v>
       </c>
       <c r="E21" t="n">
-        <v>1.9039</v>
+        <v>2.4627</v>
       </c>
       <c r="F21" t="n">
-        <v>2.7024</v>
+        <v>2.9439</v>
       </c>
       <c r="G21" t="n">
         <v>2.6748</v>
@@ -2092,13 +2092,13 @@
         <v>1.9576</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1061</v>
+        <v>0.9064</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4795</v>
+        <v>0.0793</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5856</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="V21" t="n">
         <v>0.9554</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>4.3329</v>
+        <v>4.7105</v>
       </c>
       <c r="E22" t="n">
-        <v>1.926</v>
+        <v>2.1495</v>
       </c>
       <c r="F22" t="n">
-        <v>2.4069</v>
+        <v>2.561</v>
       </c>
       <c r="G22" t="n">
         <v>1.7146</v>
@@ -2170,13 +2170,13 @@
         <v>1.7401</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2518</v>
+        <v>0.1259</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.274</v>
+        <v>-0.0505</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0222</v>
+        <v>0.1763</v>
       </c>
       <c r="V22" t="n">
         <v>1.13</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3.8857</v>
+        <v>4.5601</v>
       </c>
       <c r="E23" t="n">
-        <v>2.3389</v>
+        <v>2.6742</v>
       </c>
       <c r="F23" t="n">
-        <v>1.5468</v>
+        <v>1.8859</v>
       </c>
       <c r="G23" t="n">
         <v>3.9337</v>
@@ -2248,13 +2248,13 @@
         <v>2.1751</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.918</v>
+        <v>-0.2436</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.548</v>
+        <v>-0.2127</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.37</v>
+        <v>-0.031</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>3.8599</v>
+        <v>4.0333</v>
       </c>
       <c r="E24" t="n">
-        <v>1.6741</v>
+        <v>1.7859</v>
       </c>
       <c r="F24" t="n">
-        <v>2.1857</v>
+        <v>2.2474</v>
       </c>
       <c r="G24" t="n">
         <v>2.9216</v>
@@ -2326,13 +2326,13 @@
         <v>1.7401</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4744</v>
+        <v>-0.301</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.411</v>
+        <v>-0.2992</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0635</v>
+        <v>-0.0018</v>
       </c>
       <c r="V24" t="n">
         <v>0.7602</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. SPEIGHT</t>
+          <t>A. GALAN POZO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>3.3195</v>
+        <v>3.7771</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.6119</v>
+        <v>2.1815</v>
       </c>
       <c r="F25" t="n">
-        <v>3.9315</v>
+        <v>1.5956</v>
       </c>
       <c r="G25" t="n">
-        <v>2.1653</v>
+        <v>1.6735</v>
       </c>
       <c r="H25" t="n">
-        <v>1.986</v>
+        <v>-0.2796</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1793</v>
+        <v>1.9531</v>
       </c>
       <c r="J25" t="n">
-        <v>1.3781</v>
+        <v>0.4193</v>
       </c>
       <c r="K25" t="n">
-        <v>0.8609</v>
+        <v>-0.9577</v>
       </c>
       <c r="L25" t="n">
-        <v>0.5172</v>
+        <v>1.377</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7872</v>
+        <v>1.2542</v>
       </c>
       <c r="N25" t="n">
-        <v>1.1251</v>
+        <v>0.6781</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.3379</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>0.435</v>
+        <v>1.7401</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.3926</v>
+        <v>-0.2175</v>
       </c>
       <c r="R25" t="n">
-        <v>2.8276</v>
+        <v>1.9576</v>
       </c>
       <c r="S25" t="n">
-        <v>0.7192</v>
+        <v>0.9286</v>
       </c>
       <c r="T25" t="n">
-        <v>0.4026</v>
+        <v>0.2848</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3166</v>
+        <v>0.6438</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.695</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-2.2599</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A. GALAN POZO</t>
+          <t>M. SPEIGHT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>3.1618</v>
+        <v>2.9419</v>
       </c>
       <c r="E26" t="n">
-        <v>1.6227</v>
+        <v>-0.8355</v>
       </c>
       <c r="F26" t="n">
-        <v>1.5391</v>
+        <v>3.7773</v>
       </c>
       <c r="G26" t="n">
-        <v>1.6735</v>
+        <v>2.1653</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.2796</v>
+        <v>1.986</v>
       </c>
       <c r="I26" t="n">
-        <v>1.9531</v>
+        <v>0.1793</v>
       </c>
       <c r="J26" t="n">
-        <v>0.4193</v>
+        <v>1.3781</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.9577</v>
+        <v>0.8609</v>
       </c>
       <c r="L26" t="n">
-        <v>1.377</v>
+        <v>0.5172</v>
       </c>
       <c r="M26" t="n">
-        <v>1.2542</v>
+        <v>0.7872</v>
       </c>
       <c r="N26" t="n">
-        <v>0.6781</v>
+        <v>1.1251</v>
       </c>
       <c r="O26" t="n">
-        <v>0.5760999999999999</v>
+        <v>-0.3379</v>
       </c>
       <c r="P26" t="n">
-        <v>1.7401</v>
+        <v>0.435</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.2175</v>
+        <v>-2.3926</v>
       </c>
       <c r="R26" t="n">
-        <v>1.9576</v>
+        <v>2.8276</v>
       </c>
       <c r="S26" t="n">
-        <v>0.3133</v>
+        <v>0.3416</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.274</v>
+        <v>0.1791</v>
       </c>
       <c r="U26" t="n">
-        <v>0.5873</v>
+        <v>0.1625</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.695</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.2599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>68.91840000000001</v>
+        <v>70.40849999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>27.9813</v>
+        <v>27.9814</v>
       </c>
       <c r="F27" t="n">
-        <v>40.93699999999999</v>
+        <v>42.42709999999999</v>
       </c>
       <c r="G27" t="n">
         <v>42.8004</v>
@@ -2560,13 +2560,13 @@
         <v>30.4512</v>
       </c>
       <c r="S27" t="n">
-        <v>4.0495</v>
+        <v>5.539800000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>1.6282</v>
+        <v>1.6284</v>
       </c>
       <c r="U27" t="n">
-        <v>2.4212</v>
+        <v>3.9114</v>
       </c>
       <c r="V27" t="n">
         <v>7.930400000000001</v>
